--- a/H5509_V2/bin/Debug/Logs/202610/Log_20261020-143155.xlsx
+++ b/H5509_V2/bin/Debug/Logs/202610/Log_20261020-143155.xlsx
@@ -935,6 +935,18 @@
   </x:si>
   <x:si>
     <x:t>PS抓盘手臂放空盘到Auto2流程.Processing=False;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2026-10-20 14:44:51]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\工作\东莞思创汇\项目7\H5509_V2 - 1.1.28 延时300改为900\H5509_V2 - 1.1.28 延时300改为900\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
+   在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\工作\东莞思创汇\项目7\H5509_V2 - 1.1.28 延时300改为900\H5509_V2 - 1.1.28 延时300改为900\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2026-10-20 14:48:58]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\工作\东莞思创汇\项目7\H5509_V2 - 1.1.28 延时300改为900\H5509_V2 - 1.1.28 延时300改为900\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
+   在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\工作\东莞思创汇\项目7\H5509_V2 - 1.1.28 延时300改为900\H5509_V2 - 1.1.28 延时300改为900\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5513,6 +5525,8378 @@
         <x:v>305</x:v>
       </x:c>
     </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="1">
+        <x:v>46315.6144833449</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D302" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="1">
+        <x:v>46315.6144837963</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D303" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="1">
+        <x:v>46315.6144841898</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D304" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:4">
+      <x:c r="A305" s="1">
+        <x:v>46315.614485544</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D305" s="2" t="s">
+        <x:v>306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:4">
+      <x:c r="A306" s="1">
+        <x:v>46315.6146159838</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D306" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:4">
+      <x:c r="A307" s="1">
+        <x:v>46315.6163232755</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D307" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:4">
+      <x:c r="A308" s="1">
+        <x:v>46315.6163237384</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D308" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:4">
+      <x:c r="A309" s="1">
+        <x:v>46315.6163240856</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D309" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:4">
+      <x:c r="A310" s="1">
+        <x:v>46315.6163244676</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D310" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:4">
+      <x:c r="A311" s="1">
+        <x:v>46315.6163248264</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D311" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:4">
+      <x:c r="A312" s="1">
+        <x:v>46315.6163251852</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D312" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:4">
+      <x:c r="A313" s="1">
+        <x:v>46315.6163255556</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D313" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:4">
+      <x:c r="A314" s="1">
+        <x:v>46315.6163259144</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D314" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:4">
+      <x:c r="A315" s="1">
+        <x:v>46315.6163262963</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D315" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:4">
+      <x:c r="A316" s="1">
+        <x:v>46315.6163266551</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D316" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:4">
+      <x:c r="A317" s="1">
+        <x:v>46315.6163270139</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D317" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:4">
+      <x:c r="A318" s="1">
+        <x:v>46315.6163273727</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D318" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:4">
+      <x:c r="A319" s="1">
+        <x:v>46315.6163277315</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D319" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:4">
+      <x:c r="A320" s="1">
+        <x:v>46315.6163282639</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D320" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:4">
+      <x:c r="A321" s="1">
+        <x:v>46315.6163286227</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D321" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:4">
+      <x:c r="A322" s="1">
+        <x:v>46315.6163289815</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D322" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:4">
+      <x:c r="A323" s="1">
+        <x:v>46315.6163293403</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D323" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:4">
+      <x:c r="A324" s="1">
+        <x:v>46315.6163297106</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D324" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:4">
+      <x:c r="A325" s="1">
+        <x:v>46315.6163300694</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D325" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:4">
+      <x:c r="A326" s="1">
+        <x:v>46315.6163304167</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D326" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:4">
+      <x:c r="A327" s="1">
+        <x:v>46315.6163307755</x:v>
+      </x:c>
+      <x:c r="B327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C327" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D327" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:4">
+      <x:c r="A328" s="1">
+        <x:v>46315.6163311458</x:v>
+      </x:c>
+      <x:c r="B328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C328" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D328" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:4">
+      <x:c r="A329" s="1">
+        <x:v>46315.6163315046</x:v>
+      </x:c>
+      <x:c r="B329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C329" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D329" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:4">
+      <x:c r="A330" s="1">
+        <x:v>46315.6163318634</x:v>
+      </x:c>
+      <x:c r="B330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D330" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:4">
+      <x:c r="A331" s="1">
+        <x:v>46315.6163322222</x:v>
+      </x:c>
+      <x:c r="B331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C331" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D331" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:4">
+      <x:c r="A332" s="1">
+        <x:v>46315.6163327431</x:v>
+      </x:c>
+      <x:c r="B332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C332" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D332" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:4">
+      <x:c r="A333" s="1">
+        <x:v>46315.6163331134</x:v>
+      </x:c>
+      <x:c r="B333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C333" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D333" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:4">
+      <x:c r="A334" s="1">
+        <x:v>46315.6163334838</x:v>
+      </x:c>
+      <x:c r="B334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C334" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D334" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:4">
+      <x:c r="A335" s="1">
+        <x:v>46315.616333831</x:v>
+      </x:c>
+      <x:c r="B335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C335" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D335" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:4">
+      <x:c r="A336" s="1">
+        <x:v>46315.6163341898</x:v>
+      </x:c>
+      <x:c r="B336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C336" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D336" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:4">
+      <x:c r="A337" s="1">
+        <x:v>46315.6163345486</x:v>
+      </x:c>
+      <x:c r="B337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C337" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D337" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:4">
+      <x:c r="A338" s="1">
+        <x:v>46315.6163349074</x:v>
+      </x:c>
+      <x:c r="B338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C338" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D338" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:4">
+      <x:c r="A339" s="1">
+        <x:v>46315.6163352778</x:v>
+      </x:c>
+      <x:c r="B339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C339" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D339" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:4">
+      <x:c r="A340" s="1">
+        <x:v>46315.616335625</x:v>
+      </x:c>
+      <x:c r="B340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C340" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D340" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:4">
+      <x:c r="A341" s="1">
+        <x:v>46315.6163359838</x:v>
+      </x:c>
+      <x:c r="B341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C341" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D341" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:4">
+      <x:c r="A342" s="1">
+        <x:v>46315.6163363426</x:v>
+      </x:c>
+      <x:c r="B342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C342" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D342" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:4">
+      <x:c r="A343" s="1">
+        <x:v>46315.6163366898</x:v>
+      </x:c>
+      <x:c r="B343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C343" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D343" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:4">
+      <x:c r="A344" s="1">
+        <x:v>46315.6163370602</x:v>
+      </x:c>
+      <x:c r="B344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C344" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D344" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:4">
+      <x:c r="A345" s="1">
+        <x:v>46315.616337419</x:v>
+      </x:c>
+      <x:c r="B345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C345" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D345" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:4">
+      <x:c r="A346" s="1">
+        <x:v>46315.6163381134</x:v>
+      </x:c>
+      <x:c r="B346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C346" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D346" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:4">
+      <x:c r="A347" s="1">
+        <x:v>46315.6163384722</x:v>
+      </x:c>
+      <x:c r="B347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C347" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D347" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:4">
+      <x:c r="A348" s="1">
+        <x:v>46315.6163391782</x:v>
+      </x:c>
+      <x:c r="B348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C348" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D348" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:4">
+      <x:c r="A349" s="1">
+        <x:v>46315.6163397107</x:v>
+      </x:c>
+      <x:c r="B349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C349" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D349" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:4">
+      <x:c r="A350" s="1">
+        <x:v>46315.616340081</x:v>
+      </x:c>
+      <x:c r="B350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C350" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D350" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:4">
+      <x:c r="A351" s="1">
+        <x:v>46315.6163404398</x:v>
+      </x:c>
+      <x:c r="B351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C351" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D351" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:4">
+      <x:c r="A352" s="1">
+        <x:v>46315.616341169</x:v>
+      </x:c>
+      <x:c r="B352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D352" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:4">
+      <x:c r="A353" s="1">
+        <x:v>46315.6163415162</x:v>
+      </x:c>
+      <x:c r="B353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C353" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D353" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:4">
+      <x:c r="A354" s="1">
+        <x:v>46315.616341875</x:v>
+      </x:c>
+      <x:c r="B354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C354" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D354" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:4">
+      <x:c r="A355" s="1">
+        <x:v>46315.6163422338</x:v>
+      </x:c>
+      <x:c r="B355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C355" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D355" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:4">
+      <x:c r="A356" s="1">
+        <x:v>46315.616342581</x:v>
+      </x:c>
+      <x:c r="B356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D356" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:4">
+      <x:c r="A357" s="1">
+        <x:v>46315.6163429514</x:v>
+      </x:c>
+      <x:c r="B357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C357" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D357" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:4">
+      <x:c r="A358" s="1">
+        <x:v>46315.6163433102</x:v>
+      </x:c>
+      <x:c r="B358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C358" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D358" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:4">
+      <x:c r="A359" s="1">
+        <x:v>46315.6163436921</x:v>
+      </x:c>
+      <x:c r="B359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C359" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D359" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:4">
+      <x:c r="A360" s="1">
+        <x:v>46315.6163440509</x:v>
+      </x:c>
+      <x:c r="B360" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C360" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D360" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:4">
+      <x:c r="A361" s="1">
+        <x:v>46315.6163444097</x:v>
+      </x:c>
+      <x:c r="B361" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C361" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D361" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:4">
+      <x:c r="A362" s="1">
+        <x:v>46315.6163447685</x:v>
+      </x:c>
+      <x:c r="B362" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C362" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D362" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:4">
+      <x:c r="A363" s="1">
+        <x:v>46315.6163451389</x:v>
+      </x:c>
+      <x:c r="B363" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C363" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D363" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:4">
+      <x:c r="A364" s="1">
+        <x:v>46315.6163454861</x:v>
+      </x:c>
+      <x:c r="B364" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C364" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D364" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:4">
+      <x:c r="A365" s="1">
+        <x:v>46315.6163458333</x:v>
+      </x:c>
+      <x:c r="B365" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C365" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D365" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:4">
+      <x:c r="A366" s="1">
+        <x:v>46315.6163461921</x:v>
+      </x:c>
+      <x:c r="B366" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C366" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D366" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:4">
+      <x:c r="A367" s="1">
+        <x:v>46315.6163465509</x:v>
+      </x:c>
+      <x:c r="B367" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C367" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D367" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:4">
+      <x:c r="A368" s="1">
+        <x:v>46315.6163468981</x:v>
+      </x:c>
+      <x:c r="B368" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C368" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D368" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:4">
+      <x:c r="A369" s="1">
+        <x:v>46315.6163472569</x:v>
+      </x:c>
+      <x:c r="B369" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C369" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D369" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:4">
+      <x:c r="A370" s="1">
+        <x:v>46315.6163477893</x:v>
+      </x:c>
+      <x:c r="B370" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C370" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D370" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:4">
+      <x:c r="A371" s="1">
+        <x:v>46315.6163481481</x:v>
+      </x:c>
+      <x:c r="B371" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C371" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D371" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:4">
+      <x:c r="A372" s="1">
+        <x:v>46315.6163485185</x:v>
+      </x:c>
+      <x:c r="B372" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C372" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D372" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:4">
+      <x:c r="A373" s="1">
+        <x:v>46315.6163488657</x:v>
+      </x:c>
+      <x:c r="B373" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C373" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D373" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:4">
+      <x:c r="A374" s="1">
+        <x:v>46315.6163492361</x:v>
+      </x:c>
+      <x:c r="B374" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C374" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D374" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:4">
+      <x:c r="A375" s="1">
+        <x:v>46315.6163495833</x:v>
+      </x:c>
+      <x:c r="B375" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C375" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D375" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:4">
+      <x:c r="A376" s="1">
+        <x:v>46315.6163499537</x:v>
+      </x:c>
+      <x:c r="B376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D376" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:4">
+      <x:c r="A377" s="1">
+        <x:v>46315.6163503125</x:v>
+      </x:c>
+      <x:c r="B377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C377" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D377" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:4">
+      <x:c r="A378" s="1">
+        <x:v>46315.6163506713</x:v>
+      </x:c>
+      <x:c r="B378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C378" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D378" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:4">
+      <x:c r="A379" s="1">
+        <x:v>46315.6163510417</x:v>
+      </x:c>
+      <x:c r="B379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C379" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D379" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:4">
+      <x:c r="A380" s="1">
+        <x:v>46315.6163514005</x:v>
+      </x:c>
+      <x:c r="B380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D380" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:4">
+      <x:c r="A381" s="1">
+        <x:v>46315.6163517708</x:v>
+      </x:c>
+      <x:c r="B381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C381" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D381" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:4">
+      <x:c r="A382" s="1">
+        <x:v>46315.6163521065</x:v>
+      </x:c>
+      <x:c r="B382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D382" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:4">
+      <x:c r="A383" s="1">
+        <x:v>46315.6163524653</x:v>
+      </x:c>
+      <x:c r="B383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C383" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D383" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:4">
+      <x:c r="A384" s="1">
+        <x:v>46315.6163528241</x:v>
+      </x:c>
+      <x:c r="B384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D384" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:4">
+      <x:c r="A385" s="1">
+        <x:v>46315.6163531829</x:v>
+      </x:c>
+      <x:c r="B385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C385" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D385" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:4">
+      <x:c r="A386" s="1">
+        <x:v>46315.6163537153</x:v>
+      </x:c>
+      <x:c r="B386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C386" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D386" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:4">
+      <x:c r="A387" s="1">
+        <x:v>46315.6163542477</x:v>
+      </x:c>
+      <x:c r="B387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C387" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D387" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:4">
+      <x:c r="A388" s="1">
+        <x:v>46315.6163546181</x:v>
+      </x:c>
+      <x:c r="B388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C388" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D388" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:4">
+      <x:c r="A389" s="1">
+        <x:v>46315.6163549769</x:v>
+      </x:c>
+      <x:c r="B389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C389" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D389" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:4">
+      <x:c r="A390" s="1">
+        <x:v>46315.6163553472</x:v>
+      </x:c>
+      <x:c r="B390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C390" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D390" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:4">
+      <x:c r="A391" s="1">
+        <x:v>46315.616355706</x:v>
+      </x:c>
+      <x:c r="B391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C391" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D391" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:4">
+      <x:c r="A392" s="1">
+        <x:v>46315.6163560764</x:v>
+      </x:c>
+      <x:c r="B392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D392" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:4">
+      <x:c r="A393" s="1">
+        <x:v>46315.6163564236</x:v>
+      </x:c>
+      <x:c r="B393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C393" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D393" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:4">
+      <x:c r="A394" s="1">
+        <x:v>46315.6163567708</x:v>
+      </x:c>
+      <x:c r="B394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C394" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D394" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:4">
+      <x:c r="A395" s="1">
+        <x:v>46315.6163571296</x:v>
+      </x:c>
+      <x:c r="B395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C395" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D395" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:4">
+      <x:c r="A396" s="1">
+        <x:v>46315.616357662</x:v>
+      </x:c>
+      <x:c r="B396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D396" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:4">
+      <x:c r="A397" s="1">
+        <x:v>46315.6163580324</x:v>
+      </x:c>
+      <x:c r="B397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C397" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D397" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:4">
+      <x:c r="A398" s="1">
+        <x:v>46315.6163584028</x:v>
+      </x:c>
+      <x:c r="B398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C398" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D398" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:4">
+      <x:c r="A399" s="1">
+        <x:v>46315.6163587731</x:v>
+      </x:c>
+      <x:c r="B399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C399" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D399" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:4">
+      <x:c r="A400" s="1">
+        <x:v>46315.6163591319</x:v>
+      </x:c>
+      <x:c r="B400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D400" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:4">
+      <x:c r="A401" s="1">
+        <x:v>46315.6163594907</x:v>
+      </x:c>
+      <x:c r="B401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C401" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D401" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:4">
+      <x:c r="A402" s="1">
+        <x:v>46315.6163598611</x:v>
+      </x:c>
+      <x:c r="B402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C402" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D402" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:4">
+      <x:c r="A403" s="1">
+        <x:v>46315.6163602083</x:v>
+      </x:c>
+      <x:c r="B403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C403" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D403" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:4">
+      <x:c r="A404" s="1">
+        <x:v>46315.6163605671</x:v>
+      </x:c>
+      <x:c r="B404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D404" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:4">
+      <x:c r="A405" s="1">
+        <x:v>46315.6163609259</x:v>
+      </x:c>
+      <x:c r="B405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C405" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D405" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:4">
+      <x:c r="A406" s="1">
+        <x:v>46315.6163612616</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D406" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:4">
+      <x:c r="A407" s="1">
+        <x:v>46315.6163616319</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D407" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:4">
+      <x:c r="A408" s="1">
+        <x:v>46315.6163619907</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D408" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:4">
+      <x:c r="A409" s="1">
+        <x:v>46315.616362338</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D409" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:4">
+      <x:c r="A410" s="1">
+        <x:v>46315.6163626852</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D410" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:4">
+      <x:c r="A411" s="1">
+        <x:v>46315.616363044</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D411" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:4">
+      <x:c r="A412" s="1">
+        <x:v>46315.6163634028</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D412" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:4">
+      <x:c r="A413" s="1">
+        <x:v>46315.61636375</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D413" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:4">
+      <x:c r="A414" s="1">
+        <x:v>46315.6163641088</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D414" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:4">
+      <x:c r="A415" s="1">
+        <x:v>46315.6163644676</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D415" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:4">
+      <x:c r="A416" s="1">
+        <x:v>46315.616364838</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D416" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:4">
+      <x:c r="A417" s="1">
+        <x:v>46315.6163651968</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D417" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:4">
+      <x:c r="A418" s="1">
+        <x:v>46315.6163655556</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D418" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:4">
+      <x:c r="A419" s="1">
+        <x:v>46315.6163659143</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D419" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:4">
+      <x:c r="A420" s="1">
+        <x:v>46315.6163662616</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D420" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:4">
+      <x:c r="A421" s="1">
+        <x:v>46315.6163666204</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D421" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:4">
+      <x:c r="A422" s="1">
+        <x:v>46315.6163669907</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D422" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:4">
+      <x:c r="A423" s="1">
+        <x:v>46315.6163673495</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D423" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:4">
+      <x:c r="A424" s="1">
+        <x:v>46315.6163677199</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D424" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:4">
+      <x:c r="A425" s="1">
+        <x:v>46315.6163680671</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D425" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:4">
+      <x:c r="A426" s="1">
+        <x:v>46315.6163684375</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D426" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:4">
+      <x:c r="A427" s="1">
+        <x:v>46315.6163687847</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D427" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:4">
+      <x:c r="A428" s="1">
+        <x:v>46315.6163691435</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D428" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:4">
+      <x:c r="A429" s="1">
+        <x:v>46315.6163695023</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D429" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:4">
+      <x:c r="A430" s="1">
+        <x:v>46315.6163698611</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D430" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:4">
+      <x:c r="A431" s="1">
+        <x:v>46315.6163702199</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D431" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:4">
+      <x:c r="A432" s="1">
+        <x:v>46315.6163705787</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D432" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:4">
+      <x:c r="A433" s="1">
+        <x:v>46315.6163711111</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D433" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:4">
+      <x:c r="A434" s="1">
+        <x:v>46315.6163714815</x:v>
+      </x:c>
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D434" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:4">
+      <x:c r="A435" s="1">
+        <x:v>46315.6163718287</x:v>
+      </x:c>
+      <x:c r="B435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C435" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D435" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:4">
+      <x:c r="A436" s="1">
+        <x:v>46315.6163721991</x:v>
+      </x:c>
+      <x:c r="B436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C436" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D436" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:4">
+      <x:c r="A437" s="1">
+        <x:v>46315.6163725579</x:v>
+      </x:c>
+      <x:c r="B437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C437" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D437" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:4">
+      <x:c r="A438" s="1">
+        <x:v>46315.6163729051</x:v>
+      </x:c>
+      <x:c r="B438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C438" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D438" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:4">
+      <x:c r="A439" s="1">
+        <x:v>46315.6163732755</x:v>
+      </x:c>
+      <x:c r="B439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C439" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D439" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:4">
+      <x:c r="A440" s="1">
+        <x:v>46315.6163736343</x:v>
+      </x:c>
+      <x:c r="B440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C440" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D440" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:4">
+      <x:c r="A441" s="1">
+        <x:v>46315.6163739931</x:v>
+      </x:c>
+      <x:c r="B441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C441" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D441" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:4">
+      <x:c r="A442" s="1">
+        <x:v>46315.6163743519</x:v>
+      </x:c>
+      <x:c r="B442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C442" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D442" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:4">
+      <x:c r="A443" s="1">
+        <x:v>46315.6163747106</x:v>
+      </x:c>
+      <x:c r="B443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C443" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D443" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:4">
+      <x:c r="A444" s="1">
+        <x:v>46315.616375081</x:v>
+      </x:c>
+      <x:c r="B444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C444" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D444" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:4">
+      <x:c r="A445" s="1">
+        <x:v>46315.6163754398</x:v>
+      </x:c>
+      <x:c r="B445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C445" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D445" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:4">
+      <x:c r="A446" s="1">
+        <x:v>46315.6163757986</x:v>
+      </x:c>
+      <x:c r="B446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C446" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D446" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:4">
+      <x:c r="A447" s="1">
+        <x:v>46315.6163761574</x:v>
+      </x:c>
+      <x:c r="B447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C447" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D447" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:4">
+      <x:c r="A448" s="1">
+        <x:v>46315.6163765162</x:v>
+      </x:c>
+      <x:c r="B448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C448" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D448" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:4">
+      <x:c r="A449" s="1">
+        <x:v>46315.616376875</x:v>
+      </x:c>
+      <x:c r="B449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C449" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D449" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:4">
+      <x:c r="A450" s="1">
+        <x:v>46315.6163772338</x:v>
+      </x:c>
+      <x:c r="B450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C450" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D450" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:4">
+      <x:c r="A451" s="1">
+        <x:v>46315.6163777546</x:v>
+      </x:c>
+      <x:c r="B451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C451" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D451" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:4">
+      <x:c r="A452" s="1">
+        <x:v>46315.6163782986</x:v>
+      </x:c>
+      <x:c r="B452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C452" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D452" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:4">
+      <x:c r="A453" s="1">
+        <x:v>46315.6163786458</x:v>
+      </x:c>
+      <x:c r="B453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C453" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D453" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:4">
+      <x:c r="A454" s="1">
+        <x:v>46315.6163791898</x:v>
+      </x:c>
+      <x:c r="B454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C454" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D454" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:4">
+      <x:c r="A455" s="1">
+        <x:v>46315.616379537</x:v>
+      </x:c>
+      <x:c r="B455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C455" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D455" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:4">
+      <x:c r="A456" s="1">
+        <x:v>46315.6163799074</x:v>
+      </x:c>
+      <x:c r="B456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C456" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D456" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:4">
+      <x:c r="A457" s="1">
+        <x:v>46315.6163802662</x:v>
+      </x:c>
+      <x:c r="B457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C457" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D457" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:4">
+      <x:c r="A458" s="1">
+        <x:v>46315.6163806366</x:v>
+      </x:c>
+      <x:c r="B458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C458" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D458" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:4">
+      <x:c r="A459" s="1">
+        <x:v>46315.6163810069</x:v>
+      </x:c>
+      <x:c r="B459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C459" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D459" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:4">
+      <x:c r="A460" s="1">
+        <x:v>46315.6163815394</x:v>
+      </x:c>
+      <x:c r="B460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C460" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D460" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:4">
+      <x:c r="A461" s="1">
+        <x:v>46315.6163820602</x:v>
+      </x:c>
+      <x:c r="B461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C461" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D461" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:4">
+      <x:c r="A462" s="1">
+        <x:v>46315.6163825926</x:v>
+      </x:c>
+      <x:c r="B462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C462" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D462" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:4">
+      <x:c r="A463" s="1">
+        <x:v>46315.6163829514</x:v>
+      </x:c>
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D463" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:4">
+      <x:c r="A464" s="1">
+        <x:v>46315.6163832986</x:v>
+      </x:c>
+      <x:c r="B464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C464" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D464" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:4">
+      <x:c r="A465" s="1">
+        <x:v>46315.6163838194</x:v>
+      </x:c>
+      <x:c r="B465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C465" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D465" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:4">
+      <x:c r="A466" s="1">
+        <x:v>46315.6163841898</x:v>
+      </x:c>
+      <x:c r="B466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C466" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D466" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:4">
+      <x:c r="A467" s="1">
+        <x:v>46315.6163845486</x:v>
+      </x:c>
+      <x:c r="B467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C467" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D467" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:4">
+      <x:c r="A468" s="1">
+        <x:v>46315.616384919</x:v>
+      </x:c>
+      <x:c r="B468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C468" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D468" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:4">
+      <x:c r="A469" s="1">
+        <x:v>46315.6163852778</x:v>
+      </x:c>
+      <x:c r="B469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C469" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D469" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:4">
+      <x:c r="A470" s="1">
+        <x:v>46315.6163856366</x:v>
+      </x:c>
+      <x:c r="B470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C470" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D470" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:4">
+      <x:c r="A471" s="1">
+        <x:v>46315.6163861806</x:v>
+      </x:c>
+      <x:c r="B471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C471" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D471" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:4">
+      <x:c r="A472" s="1">
+        <x:v>46315.6163867014</x:v>
+      </x:c>
+      <x:c r="B472" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C472" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D472" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:4">
+      <x:c r="A473" s="1">
+        <x:v>46315.6163870602</x:v>
+      </x:c>
+      <x:c r="B473" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C473" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D473" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:4">
+      <x:c r="A474" s="1">
+        <x:v>46315.6163876042</x:v>
+      </x:c>
+      <x:c r="B474" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C474" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D474" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:4">
+      <x:c r="A475" s="1">
+        <x:v>46315.616387963</x:v>
+      </x:c>
+      <x:c r="B475" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C475" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D475" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:4">
+      <x:c r="A476" s="1">
+        <x:v>46315.6163885185</x:v>
+      </x:c>
+      <x:c r="B476" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C476" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D476" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:4">
+      <x:c r="A477" s="1">
+        <x:v>46315.6163890394</x:v>
+      </x:c>
+      <x:c r="B477" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C477" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D477" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:4">
+      <x:c r="A478" s="1">
+        <x:v>46315.6163895833</x:v>
+      </x:c>
+      <x:c r="B478" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C478" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D478" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:4">
+      <x:c r="A479" s="1">
+        <x:v>46315.6163899421</x:v>
+      </x:c>
+      <x:c r="B479" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C479" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D479" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:4">
+      <x:c r="A480" s="1">
+        <x:v>46315.6163903125</x:v>
+      </x:c>
+      <x:c r="B480" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C480" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D480" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:4">
+      <x:c r="A481" s="1">
+        <x:v>46315.6163908333</x:v>
+      </x:c>
+      <x:c r="B481" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C481" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D481" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:4">
+      <x:c r="A482" s="1">
+        <x:v>46315.6163913657</x:v>
+      </x:c>
+      <x:c r="B482" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C482" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D482" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:4">
+      <x:c r="A483" s="1">
+        <x:v>46315.6163918056</x:v>
+      </x:c>
+      <x:c r="B483" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C483" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D483" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:4">
+      <x:c r="A484" s="1">
+        <x:v>46315.6163923148</x:v>
+      </x:c>
+      <x:c r="B484" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C484" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D484" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:4">
+      <x:c r="A485" s="1">
+        <x:v>46315.6163928009</x:v>
+      </x:c>
+      <x:c r="B485" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C485" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D485" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:4">
+      <x:c r="A486" s="1">
+        <x:v>46315.6163931597</x:v>
+      </x:c>
+      <x:c r="B486" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C486" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D486" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:4">
+      <x:c r="A487" s="1">
+        <x:v>46315.6163935069</x:v>
+      </x:c>
+      <x:c r="B487" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C487" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D487" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:4">
+      <x:c r="A488" s="1">
+        <x:v>46315.6163938773</x:v>
+      </x:c>
+      <x:c r="B488" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C488" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D488" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:4">
+      <x:c r="A489" s="1">
+        <x:v>46315.6163942245</x:v>
+      </x:c>
+      <x:c r="B489" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C489" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D489" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:4">
+      <x:c r="A490" s="1">
+        <x:v>46315.6163945833</x:v>
+      </x:c>
+      <x:c r="B490" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C490" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D490" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:4">
+      <x:c r="A491" s="1">
+        <x:v>46315.6163949421</x:v>
+      </x:c>
+      <x:c r="B491" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C491" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D491" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:4">
+      <x:c r="A492" s="1">
+        <x:v>46315.6163953125</x:v>
+      </x:c>
+      <x:c r="B492" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C492" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D492" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:4">
+      <x:c r="A493" s="1">
+        <x:v>46315.6163956597</x:v>
+      </x:c>
+      <x:c r="B493" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C493" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D493" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:4">
+      <x:c r="A494" s="1">
+        <x:v>46315.6163962037</x:v>
+      </x:c>
+      <x:c r="B494" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C494" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D494" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:4">
+      <x:c r="A495" s="1">
+        <x:v>46315.6163967361</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D495" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:4">
+      <x:c r="A496" s="1">
+        <x:v>46315.6163971065</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D496" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:4">
+      <x:c r="A497" s="1">
+        <x:v>46315.6163974537</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D497" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:4">
+      <x:c r="A498" s="1">
+        <x:v>46315.6163978125</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D498" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:4">
+      <x:c r="A499" s="1">
+        <x:v>46315.6163981713</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D499" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:4">
+      <x:c r="A500" s="1">
+        <x:v>46315.6163985417</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D500" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:4">
+      <x:c r="A501" s="1">
+        <x:v>46315.6163989005</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D501" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:4">
+      <x:c r="A502" s="1">
+        <x:v>46315.6163994213</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D502" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:4">
+      <x:c r="A503" s="1">
+        <x:v>46315.6163997801</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D503" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:4">
+      <x:c r="A504" s="1">
+        <x:v>46315.6164001389</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D504" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:4">
+      <x:c r="A505" s="1">
+        <x:v>46315.6164004977</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D505" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:4">
+      <x:c r="A506" s="1">
+        <x:v>46315.6164010417</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D506" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:4">
+      <x:c r="A507" s="1">
+        <x:v>46315.6164014005</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D507" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:4">
+      <x:c r="A508" s="1">
+        <x:v>46315.6164017593</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D508" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:4">
+      <x:c r="A509" s="1">
+        <x:v>46315.6164021181</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D509" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:4">
+      <x:c r="A510" s="1">
+        <x:v>46315.6164024769</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D510" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:4">
+      <x:c r="A511" s="1">
+        <x:v>46315.6164028241</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D511" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:4">
+      <x:c r="A512" s="1">
+        <x:v>46315.6164031829</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D512" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:4">
+      <x:c r="A513" s="1">
+        <x:v>46315.6164035417</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D513" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:4">
+      <x:c r="A514" s="1">
+        <x:v>46315.6164039005</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D514" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:4">
+      <x:c r="A515" s="1">
+        <x:v>46315.6164044329</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D515" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:4">
+      <x:c r="A516" s="1">
+        <x:v>46315.6164047801</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D516" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:4">
+      <x:c r="A517" s="1">
+        <x:v>46315.6164053125</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D517" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:4">
+      <x:c r="A518" s="1">
+        <x:v>46315.6164056713</x:v>
+      </x:c>
+      <x:c r="B518" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C518" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D518" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:4">
+      <x:c r="A519" s="1">
+        <x:v>46315.6164060301</x:v>
+      </x:c>
+      <x:c r="B519" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C519" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D519" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:4">
+      <x:c r="A520" s="1">
+        <x:v>46315.6164063889</x:v>
+      </x:c>
+      <x:c r="B520" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C520" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D520" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:4">
+      <x:c r="A521" s="1">
+        <x:v>46315.6164067477</x:v>
+      </x:c>
+      <x:c r="B521" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C521" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D521" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:4">
+      <x:c r="A522" s="1">
+        <x:v>46315.6164072801</x:v>
+      </x:c>
+      <x:c r="B522" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D522" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:4">
+      <x:c r="A523" s="1">
+        <x:v>46315.6164078125</x:v>
+      </x:c>
+      <x:c r="B523" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C523" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D523" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:4">
+      <x:c r="A524" s="1">
+        <x:v>46315.6164081829</x:v>
+      </x:c>
+      <x:c r="B524" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C524" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D524" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:4">
+      <x:c r="A525" s="1">
+        <x:v>46315.6164085301</x:v>
+      </x:c>
+      <x:c r="B525" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C525" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D525" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:4">
+      <x:c r="A526" s="1">
+        <x:v>46315.6164088889</x:v>
+      </x:c>
+      <x:c r="B526" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C526" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D526" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:4">
+      <x:c r="A527" s="1">
+        <x:v>46315.6164092361</x:v>
+      </x:c>
+      <x:c r="B527" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C527" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D527" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:4">
+      <x:c r="A528" s="1">
+        <x:v>46315.6164095949</x:v>
+      </x:c>
+      <x:c r="B528" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C528" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D528" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:4">
+      <x:c r="A529" s="1">
+        <x:v>46315.6164099421</x:v>
+      </x:c>
+      <x:c r="B529" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C529" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D529" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:4">
+      <x:c r="A530" s="1">
+        <x:v>46315.6164103009</x:v>
+      </x:c>
+      <x:c r="B530" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C530" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D530" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:4">
+      <x:c r="A531" s="1">
+        <x:v>46315.6164106713</x:v>
+      </x:c>
+      <x:c r="B531" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C531" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D531" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:4">
+      <x:c r="A532" s="1">
+        <x:v>46315.6164112037</x:v>
+      </x:c>
+      <x:c r="B532" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C532" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D532" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:4">
+      <x:c r="A533" s="1">
+        <x:v>46315.6164115625</x:v>
+      </x:c>
+      <x:c r="B533" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C533" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D533" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:4">
+      <x:c r="A534" s="1">
+        <x:v>46315.6164119097</x:v>
+      </x:c>
+      <x:c r="B534" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C534" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D534" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:4">
+      <x:c r="A535" s="1">
+        <x:v>46315.6164124421</x:v>
+      </x:c>
+      <x:c r="B535" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C535" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D535" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:4">
+      <x:c r="A536" s="1">
+        <x:v>46315.6164128009</x:v>
+      </x:c>
+      <x:c r="B536" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C536" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D536" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:4">
+      <x:c r="A537" s="1">
+        <x:v>46315.6164133449</x:v>
+      </x:c>
+      <x:c r="B537" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C537" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D537" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:4">
+      <x:c r="A538" s="1">
+        <x:v>46315.6164137037</x:v>
+      </x:c>
+      <x:c r="B538" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C538" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D538" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:4">
+      <x:c r="A539" s="1">
+        <x:v>46315.6164142245</x:v>
+      </x:c>
+      <x:c r="B539" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C539" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D539" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:4">
+      <x:c r="A540" s="1">
+        <x:v>46315.6164145949</x:v>
+      </x:c>
+      <x:c r="B540" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C540" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D540" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:4">
+      <x:c r="A541" s="1">
+        <x:v>46315.6164149653</x:v>
+      </x:c>
+      <x:c r="B541" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C541" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D541" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:4">
+      <x:c r="A542" s="1">
+        <x:v>46315.6164153125</x:v>
+      </x:c>
+      <x:c r="B542" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C542" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D542" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:4">
+      <x:c r="A543" s="1">
+        <x:v>46315.6164156713</x:v>
+      </x:c>
+      <x:c r="B543" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C543" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D543" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:4">
+      <x:c r="A544" s="1">
+        <x:v>46315.6164160301</x:v>
+      </x:c>
+      <x:c r="B544" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C544" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D544" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:4">
+      <x:c r="A545" s="1">
+        <x:v>46315.6164164005</x:v>
+      </x:c>
+      <x:c r="B545" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C545" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D545" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:4">
+      <x:c r="A546" s="1">
+        <x:v>46315.6164169329</x:v>
+      </x:c>
+      <x:c r="B546" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C546" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D546" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:4">
+      <x:c r="A547" s="1">
+        <x:v>46315.6164172917</x:v>
+      </x:c>
+      <x:c r="B547" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C547" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D547" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:4">
+      <x:c r="A548" s="1">
+        <x:v>46315.616417662</x:v>
+      </x:c>
+      <x:c r="B548" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C548" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D548" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:4">
+      <x:c r="A549" s="1">
+        <x:v>46315.6164180093</x:v>
+      </x:c>
+      <x:c r="B549" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C549" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D549" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:4">
+      <x:c r="A550" s="1">
+        <x:v>46315.6164185301</x:v>
+      </x:c>
+      <x:c r="B550" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C550" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D550" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:4">
+      <x:c r="A551" s="1">
+        <x:v>46315.6164190741</x:v>
+      </x:c>
+      <x:c r="B551" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C551" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D551" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:4">
+      <x:c r="A552" s="1">
+        <x:v>46315.6164196181</x:v>
+      </x:c>
+      <x:c r="B552" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C552" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D552" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:4">
+      <x:c r="A553" s="1">
+        <x:v>46315.6164199653</x:v>
+      </x:c>
+      <x:c r="B553" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C553" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D553" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:4">
+      <x:c r="A554" s="1">
+        <x:v>46315.6164203356</x:v>
+      </x:c>
+      <x:c r="B554" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C554" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D554" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:4">
+      <x:c r="A555" s="1">
+        <x:v>46315.6164206829</x:v>
+      </x:c>
+      <x:c r="B555" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C555" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D555" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:4">
+      <x:c r="A556" s="1">
+        <x:v>46315.6164212153</x:v>
+      </x:c>
+      <x:c r="B556" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C556" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D556" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:4">
+      <x:c r="A557" s="1">
+        <x:v>46315.6164215856</x:v>
+      </x:c>
+      <x:c r="B557" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C557" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D557" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:4">
+      <x:c r="A558" s="1">
+        <x:v>46315.6164221296</x:v>
+      </x:c>
+      <x:c r="B558" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C558" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D558" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:4">
+      <x:c r="A559" s="1">
+        <x:v>46315.616422662</x:v>
+      </x:c>
+      <x:c r="B559" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C559" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D559" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:4">
+      <x:c r="A560" s="1">
+        <x:v>46315.6164230208</x:v>
+      </x:c>
+      <x:c r="B560" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C560" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D560" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:4">
+      <x:c r="A561" s="1">
+        <x:v>46315.6164233796</x:v>
+      </x:c>
+      <x:c r="B561" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C561" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D561" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:4">
+      <x:c r="A562" s="1">
+        <x:v>46315.6164237384</x:v>
+      </x:c>
+      <x:c r="B562" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C562" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D562" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:4">
+      <x:c r="A563" s="1">
+        <x:v>46315.6164241088</x:v>
+      </x:c>
+      <x:c r="B563" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C563" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D563" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:4">
+      <x:c r="A564" s="1">
+        <x:v>46315.6164244676</x:v>
+      </x:c>
+      <x:c r="B564" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C564" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D564" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:4">
+      <x:c r="A565" s="1">
+        <x:v>46315.6164248264</x:v>
+      </x:c>
+      <x:c r="B565" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C565" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D565" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:4">
+      <x:c r="A566" s="1">
+        <x:v>46315.6164251968</x:v>
+      </x:c>
+      <x:c r="B566" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C566" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D566" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:4">
+      <x:c r="A567" s="1">
+        <x:v>46315.6164255556</x:v>
+      </x:c>
+      <x:c r="B567" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C567" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D567" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:4">
+      <x:c r="A568" s="1">
+        <x:v>46315.616426088</x:v>
+      </x:c>
+      <x:c r="B568" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C568" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D568" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:4">
+      <x:c r="A569" s="1">
+        <x:v>46315.6164264583</x:v>
+      </x:c>
+      <x:c r="B569" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C569" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D569" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:4">
+      <x:c r="A570" s="1">
+        <x:v>46315.6164268056</x:v>
+      </x:c>
+      <x:c r="B570" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C570" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D570" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:4">
+      <x:c r="A571" s="1">
+        <x:v>46315.6164271644</x:v>
+      </x:c>
+      <x:c r="B571" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C571" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D571" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:4">
+      <x:c r="A572" s="1">
+        <x:v>46315.6164275347</x:v>
+      </x:c>
+      <x:c r="B572" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C572" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D572" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:4">
+      <x:c r="A573" s="1">
+        <x:v>46315.6164278819</x:v>
+      </x:c>
+      <x:c r="B573" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C573" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D573" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:4">
+      <x:c r="A574" s="1">
+        <x:v>46315.6164282407</x:v>
+      </x:c>
+      <x:c r="B574" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C574" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D574" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:4">
+      <x:c r="A575" s="1">
+        <x:v>46315.6164285995</x:v>
+      </x:c>
+      <x:c r="B575" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C575" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D575" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:4">
+      <x:c r="A576" s="1">
+        <x:v>46315.6164291435</x:v>
+      </x:c>
+      <x:c r="B576" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C576" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D576" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:4">
+      <x:c r="A577" s="1">
+        <x:v>46315.6164294907</x:v>
+      </x:c>
+      <x:c r="B577" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C577" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D577" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:4">
+      <x:c r="A578" s="1">
+        <x:v>46315.6164298611</x:v>
+      </x:c>
+      <x:c r="B578" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C578" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D578" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:4">
+      <x:c r="A579" s="1">
+        <x:v>46315.6164302199</x:v>
+      </x:c>
+      <x:c r="B579" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C579" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D579" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:4">
+      <x:c r="A580" s="1">
+        <x:v>46315.6164305787</x:v>
+      </x:c>
+      <x:c r="B580" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C580" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D580" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:4">
+      <x:c r="A581" s="1">
+        <x:v>46315.6164310995</x:v>
+      </x:c>
+      <x:c r="B581" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C581" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D581" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:4">
+      <x:c r="A582" s="1">
+        <x:v>46315.6164316319</x:v>
+      </x:c>
+      <x:c r="B582" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C582" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D582" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:4">
+      <x:c r="A583" s="1">
+        <x:v>46315.6164319792</x:v>
+      </x:c>
+      <x:c r="B583" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C583" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D583" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:4">
+      <x:c r="A584" s="1">
+        <x:v>46315.6164323495</x:v>
+      </x:c>
+      <x:c r="B584" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C584" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D584" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:4">
+      <x:c r="A585" s="1">
+        <x:v>46315.6164328935</x:v>
+      </x:c>
+      <x:c r="B585" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C585" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D585" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:4">
+      <x:c r="A586" s="1">
+        <x:v>46315.6164332523</x:v>
+      </x:c>
+      <x:c r="B586" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C586" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D586" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:4">
+      <x:c r="A587" s="1">
+        <x:v>46315.6164336111</x:v>
+      </x:c>
+      <x:c r="B587" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C587" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D587" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:4">
+      <x:c r="A588" s="1">
+        <x:v>46315.6164339699</x:v>
+      </x:c>
+      <x:c r="B588" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C588" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D588" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:4">
+      <x:c r="A589" s="1">
+        <x:v>46315.6164343287</x:v>
+      </x:c>
+      <x:c r="B589" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C589" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D589" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:4">
+      <x:c r="A590" s="1">
+        <x:v>46315.6164348611</x:v>
+      </x:c>
+      <x:c r="B590" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C590" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D590" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:4">
+      <x:c r="A591" s="1">
+        <x:v>46315.6164352315</x:v>
+      </x:c>
+      <x:c r="B591" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C591" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D591" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:4">
+      <x:c r="A592" s="1">
+        <x:v>46315.6164355787</x:v>
+      </x:c>
+      <x:c r="B592" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C592" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D592" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:4">
+      <x:c r="A593" s="1">
+        <x:v>46315.6164359375</x:v>
+      </x:c>
+      <x:c r="B593" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C593" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D593" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:4">
+      <x:c r="A594" s="1">
+        <x:v>46315.6164363079</x:v>
+      </x:c>
+      <x:c r="B594" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C594" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D594" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:4">
+      <x:c r="A595" s="1">
+        <x:v>46315.6164366667</x:v>
+      </x:c>
+      <x:c r="B595" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C595" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D595" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:4">
+      <x:c r="A596" s="1">
+        <x:v>46315.6164372107</x:v>
+      </x:c>
+      <x:c r="B596" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C596" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D596" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:4">
+      <x:c r="A597" s="1">
+        <x:v>46315.6164377431</x:v>
+      </x:c>
+      <x:c r="B597" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C597" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D597" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:4">
+      <x:c r="A598" s="1">
+        <x:v>46315.616438287</x:v>
+      </x:c>
+      <x:c r="B598" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C598" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D598" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:4">
+      <x:c r="A599" s="1">
+        <x:v>46315.6164388079</x:v>
+      </x:c>
+      <x:c r="B599" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C599" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D599" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:4">
+      <x:c r="A600" s="1">
+        <x:v>46315.6164391898</x:v>
+      </x:c>
+      <x:c r="B600" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C600" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D600" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:4">
+      <x:c r="A601" s="1">
+        <x:v>46315.6173418866</x:v>
+      </x:c>
+      <x:c r="B601" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C601" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D601" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:4">
+      <x:c r="A602" s="1">
+        <x:v>46315.6173422917</x:v>
+      </x:c>
+      <x:c r="B602" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C602" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D602" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:4">
+      <x:c r="A603" s="1">
+        <x:v>46315.6173428588</x:v>
+      </x:c>
+      <x:c r="B603" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C603" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D603" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:4">
+      <x:c r="A604" s="1">
+        <x:v>46315.6173441435</x:v>
+      </x:c>
+      <x:c r="B604" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C604" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D604" s="2" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:4">
+      <x:c r="A605" s="1">
+        <x:v>46315.6174757407</x:v>
+      </x:c>
+      <x:c r="B605" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C605" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D605" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:4">
+      <x:c r="A606" s="1">
+        <x:v>46315.6196367708</x:v>
+      </x:c>
+      <x:c r="B606" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C606" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D606" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:4">
+      <x:c r="A607" s="1">
+        <x:v>46315.6196372454</x:v>
+      </x:c>
+      <x:c r="B607" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C607" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D607" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:4">
+      <x:c r="A608" s="1">
+        <x:v>46315.6196376852</x:v>
+      </x:c>
+      <x:c r="B608" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C608" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D608" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:4">
+      <x:c r="A609" s="1">
+        <x:v>46315.6196380556</x:v>
+      </x:c>
+      <x:c r="B609" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C609" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D609" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:4">
+      <x:c r="A610" s="1">
+        <x:v>46315.6196384491</x:v>
+      </x:c>
+      <x:c r="B610" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C610" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D610" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:4">
+      <x:c r="A611" s="1">
+        <x:v>46315.619638831</x:v>
+      </x:c>
+      <x:c r="B611" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C611" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D611" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:4">
+      <x:c r="A612" s="1">
+        <x:v>46315.6196392245</x:v>
+      </x:c>
+      <x:c r="B612" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C612" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D612" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:4">
+      <x:c r="A613" s="1">
+        <x:v>46315.6196395949</x:v>
+      </x:c>
+      <x:c r="B613" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C613" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D613" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:4">
+      <x:c r="A614" s="1">
+        <x:v>46315.6196401273</x:v>
+      </x:c>
+      <x:c r="B614" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C614" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D614" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:4">
+      <x:c r="A615" s="1">
+        <x:v>46315.6196404861</x:v>
+      </x:c>
+      <x:c r="B615" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C615" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D615" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:4">
+      <x:c r="A616" s="1">
+        <x:v>46315.6196408565</x:v>
+      </x:c>
+      <x:c r="B616" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C616" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D616" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:4">
+      <x:c r="A617" s="1">
+        <x:v>46315.619641331</x:v>
+      </x:c>
+      <x:c r="B617" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C617" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D617" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:4">
+      <x:c r="A618" s="1">
+        <x:v>46315.6196417014</x:v>
+      </x:c>
+      <x:c r="B618" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C618" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D618" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:4">
+      <x:c r="A619" s="1">
+        <x:v>46315.6196420718</x:v>
+      </x:c>
+      <x:c r="B619" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C619" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D619" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:4">
+      <x:c r="A620" s="1">
+        <x:v>46315.6196424653</x:v>
+      </x:c>
+      <x:c r="B620" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C620" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D620" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:4">
+      <x:c r="A621" s="1">
+        <x:v>46315.6196429514</x:v>
+      </x:c>
+      <x:c r="B621" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C621" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D621" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:4">
+      <x:c r="A622" s="1">
+        <x:v>46315.6196433449</x:v>
+      </x:c>
+      <x:c r="B622" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C622" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D622" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:4">
+      <x:c r="A623" s="1">
+        <x:v>46315.619643831</x:v>
+      </x:c>
+      <x:c r="B623" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C623" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D623" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:4">
+      <x:c r="A624" s="1">
+        <x:v>46315.6196442014</x:v>
+      </x:c>
+      <x:c r="B624" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C624" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D624" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:4">
+      <x:c r="A625" s="1">
+        <x:v>46315.6196443866</x:v>
+      </x:c>
+      <x:c r="B625" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C625" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D625" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" spans="1:4">
+      <x:c r="A626" s="1">
+        <x:v>46315.6196443866</x:v>
+      </x:c>
+      <x:c r="B626" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C626" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D626" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" spans="1:4">
+      <x:c r="A627" s="1">
+        <x:v>46315.6196443866</x:v>
+      </x:c>
+      <x:c r="B627" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C627" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D627" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" spans="1:4">
+      <x:c r="A628" s="1">
+        <x:v>46315.6196447454</x:v>
+      </x:c>
+      <x:c r="B628" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C628" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D628" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" spans="1:4">
+      <x:c r="A629" s="1">
+        <x:v>46315.6196451042</x:v>
+      </x:c>
+      <x:c r="B629" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C629" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D629" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" spans="1:4">
+      <x:c r="A630" s="1">
+        <x:v>46315.6196454977</x:v>
+      </x:c>
+      <x:c r="B630" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C630" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D630" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" spans="1:4">
+      <x:c r="A631" s="1">
+        <x:v>46315.6196458218</x:v>
+      </x:c>
+      <x:c r="B631" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C631" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D631" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" spans="1:4">
+      <x:c r="A632" s="1">
+        <x:v>46315.6196461806</x:v>
+      </x:c>
+      <x:c r="B632" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C632" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D632" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" spans="1:4">
+      <x:c r="A633" s="1">
+        <x:v>46315.6196465972</x:v>
+      </x:c>
+      <x:c r="B633" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C633" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D633" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" spans="1:4">
+      <x:c r="A634" s="1">
+        <x:v>46315.6196470255</x:v>
+      </x:c>
+      <x:c r="B634" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C634" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D634" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" spans="1:4">
+      <x:c r="A635" s="1">
+        <x:v>46315.6196473611</x:v>
+      </x:c>
+      <x:c r="B635" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C635" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D635" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" spans="1:4">
+      <x:c r="A636" s="1">
+        <x:v>46315.6196477431</x:v>
+      </x:c>
+      <x:c r="B636" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C636" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D636" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" spans="1:4">
+      <x:c r="A637" s="1">
+        <x:v>46315.6196482292</x:v>
+      </x:c>
+      <x:c r="B637" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C637" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D637" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" spans="1:4">
+      <x:c r="A638" s="1">
+        <x:v>46315.6196485995</x:v>
+      </x:c>
+      <x:c r="B638" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C638" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D638" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" spans="1:4">
+      <x:c r="A639" s="1">
+        <x:v>46315.6196489699</x:v>
+      </x:c>
+      <x:c r="B639" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C639" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D639" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" spans="1:4">
+      <x:c r="A640" s="1">
+        <x:v>46315.6196493519</x:v>
+      </x:c>
+      <x:c r="B640" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C640" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D640" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" spans="1:4">
+      <x:c r="A641" s="1">
+        <x:v>46315.6196497222</x:v>
+      </x:c>
+      <x:c r="B641" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C641" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D641" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" spans="1:4">
+      <x:c r="A642" s="1">
+        <x:v>46315.6196501042</x:v>
+      </x:c>
+      <x:c r="B642" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C642" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D642" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" spans="1:4">
+      <x:c r="A643" s="1">
+        <x:v>46315.6196504861</x:v>
+      </x:c>
+      <x:c r="B643" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C643" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D643" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" spans="1:4">
+      <x:c r="A644" s="1">
+        <x:v>46315.6196508565</x:v>
+      </x:c>
+      <x:c r="B644" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C644" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D644" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" spans="1:4">
+      <x:c r="A645" s="1">
+        <x:v>46315.61965125</x:v>
+      </x:c>
+      <x:c r="B645" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C645" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D645" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" spans="1:4">
+      <x:c r="A646" s="1">
+        <x:v>46315.6196516319</x:v>
+      </x:c>
+      <x:c r="B646" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C646" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D646" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" spans="1:4">
+      <x:c r="A647" s="1">
+        <x:v>46315.6196520949</x:v>
+      </x:c>
+      <x:c r="B647" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C647" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D647" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" spans="1:4">
+      <x:c r="A648" s="1">
+        <x:v>46315.6196524653</x:v>
+      </x:c>
+      <x:c r="B648" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C648" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D648" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" spans="1:4">
+      <x:c r="A649" s="1">
+        <x:v>46315.6196529167</x:v>
+      </x:c>
+      <x:c r="B649" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C649" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D649" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" spans="1:4">
+      <x:c r="A650" s="1">
+        <x:v>46315.6196532986</x:v>
+      </x:c>
+      <x:c r="B650" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C650" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D650" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" spans="1:4">
+      <x:c r="A651" s="1">
+        <x:v>46315.6196538079</x:v>
+      </x:c>
+      <x:c r="B651" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C651" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D651" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" spans="1:4">
+      <x:c r="A652" s="1">
+        <x:v>46315.6196542593</x:v>
+      </x:c>
+      <x:c r="B652" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C652" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D652" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" spans="1:4">
+      <x:c r="A653" s="1">
+        <x:v>46315.6196546875</x:v>
+      </x:c>
+      <x:c r="B653" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C653" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D653" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" spans="1:4">
+      <x:c r="A654" s="1">
+        <x:v>46315.6196550579</x:v>
+      </x:c>
+      <x:c r="B654" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C654" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D654" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" spans="1:4">
+      <x:c r="A655" s="1">
+        <x:v>46315.6196554282</x:v>
+      </x:c>
+      <x:c r="B655" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C655" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D655" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" spans="1:4">
+      <x:c r="A656" s="1">
+        <x:v>46315.6196558102</x:v>
+      </x:c>
+      <x:c r="B656" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C656" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D656" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" spans="1:4">
+      <x:c r="A657" s="1">
+        <x:v>46315.6196561806</x:v>
+      </x:c>
+      <x:c r="B657" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C657" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D657" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" spans="1:4">
+      <x:c r="A658" s="1">
+        <x:v>46315.6196566088</x:v>
+      </x:c>
+      <x:c r="B658" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C658" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D658" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" spans="1:4">
+      <x:c r="A659" s="1">
+        <x:v>46315.619657037</x:v>
+      </x:c>
+      <x:c r="B659" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C659" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D659" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" spans="1:4">
+      <x:c r="A660" s="1">
+        <x:v>46315.6196575463</x:v>
+      </x:c>
+      <x:c r="B660" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C660" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D660" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" spans="1:4">
+      <x:c r="A661" s="1">
+        <x:v>46315.6196580787</x:v>
+      </x:c>
+      <x:c r="B661" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C661" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D661" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" spans="1:4">
+      <x:c r="A662" s="1">
+        <x:v>46315.6196584491</x:v>
+      </x:c>
+      <x:c r="B662" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C662" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D662" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" spans="1:4">
+      <x:c r="A663" s="1">
+        <x:v>46315.619658831</x:v>
+      </x:c>
+      <x:c r="B663" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C663" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D663" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" spans="1:4">
+      <x:c r="A664" s="1">
+        <x:v>46315.619659213</x:v>
+      </x:c>
+      <x:c r="B664" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C664" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D664" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" spans="1:4">
+      <x:c r="A665" s="1">
+        <x:v>46315.6196597685</x:v>
+      </x:c>
+      <x:c r="B665" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C665" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D665" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" spans="1:4">
+      <x:c r="A666" s="1">
+        <x:v>46315.6196601389</x:v>
+      </x:c>
+      <x:c r="B666" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C666" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D666" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" spans="1:4">
+      <x:c r="A667" s="1">
+        <x:v>46315.6196606134</x:v>
+      </x:c>
+      <x:c r="B667" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C667" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D667" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" spans="1:4">
+      <x:c r="A668" s="1">
+        <x:v>46315.6196610648</x:v>
+      </x:c>
+      <x:c r="B668" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C668" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D668" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" spans="1:4">
+      <x:c r="A669" s="1">
+        <x:v>46315.6196614468</x:v>
+      </x:c>
+      <x:c r="B669" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C669" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D669" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" spans="1:4">
+      <x:c r="A670" s="1">
+        <x:v>46315.6196618866</x:v>
+      </x:c>
+      <x:c r="B670" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C670" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D670" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" spans="1:4">
+      <x:c r="A671" s="1">
+        <x:v>46315.6196622569</x:v>
+      </x:c>
+      <x:c r="B671" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C671" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D671" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" spans="1:4">
+      <x:c r="A672" s="1">
+        <x:v>46315.619662581</x:v>
+      </x:c>
+      <x:c r="B672" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C672" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D672" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" spans="1:4">
+      <x:c r="A673" s="1">
+        <x:v>46315.619663044</x:v>
+      </x:c>
+      <x:c r="B673" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C673" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D673" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" spans="1:4">
+      <x:c r="A674" s="1">
+        <x:v>46315.6196634491</x:v>
+      </x:c>
+      <x:c r="B674" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C674" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D674" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" spans="1:4">
+      <x:c r="A675" s="1">
+        <x:v>46315.6196639699</x:v>
+      </x:c>
+      <x:c r="B675" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C675" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D675" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" spans="1:4">
+      <x:c r="A676" s="1">
+        <x:v>46315.6196643287</x:v>
+      </x:c>
+      <x:c r="B676" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C676" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D676" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" spans="1:4">
+      <x:c r="A677" s="1">
+        <x:v>46315.6196647801</x:v>
+      </x:c>
+      <x:c r="B677" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C677" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D677" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" spans="1:4">
+      <x:c r="A678" s="1">
+        <x:v>46315.6196652199</x:v>
+      </x:c>
+      <x:c r="B678" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C678" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D678" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" spans="1:4">
+      <x:c r="A679" s="1">
+        <x:v>46315.6196656713</x:v>
+      </x:c>
+      <x:c r="B679" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C679" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D679" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" spans="1:4">
+      <x:c r="A680" s="1">
+        <x:v>46315.6196660532</x:v>
+      </x:c>
+      <x:c r="B680" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C680" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D680" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" spans="1:4">
+      <x:c r="A681" s="1">
+        <x:v>46315.6196664583</x:v>
+      </x:c>
+      <x:c r="B681" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C681" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D681" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" spans="1:4">
+      <x:c r="A682" s="1">
+        <x:v>46315.619666875</x:v>
+      </x:c>
+      <x:c r="B682" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C682" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D682" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" spans="1:4">
+      <x:c r="A683" s="1">
+        <x:v>46315.6196672454</x:v>
+      </x:c>
+      <x:c r="B683" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C683" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D683" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" spans="1:4">
+      <x:c r="A684" s="1">
+        <x:v>46315.6196677546</x:v>
+      </x:c>
+      <x:c r="B684" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C684" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D684" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" spans="1:4">
+      <x:c r="A685" s="1">
+        <x:v>46315.6196681597</x:v>
+      </x:c>
+      <x:c r="B685" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C685" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D685" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" spans="1:4">
+      <x:c r="A686" s="1">
+        <x:v>46315.6196685532</x:v>
+      </x:c>
+      <x:c r="B686" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C686" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D686" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" spans="1:4">
+      <x:c r="A687" s="1">
+        <x:v>46315.6196689699</x:v>
+      </x:c>
+      <x:c r="B687" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C687" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D687" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" spans="1:4">
+      <x:c r="A688" s="1">
+        <x:v>46315.6196693287</x:v>
+      </x:c>
+      <x:c r="B688" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C688" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D688" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" spans="1:4">
+      <x:c r="A689" s="1">
+        <x:v>46315.6196697801</x:v>
+      </x:c>
+      <x:c r="B689" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C689" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D689" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" spans="1:4">
+      <x:c r="A690" s="1">
+        <x:v>46315.6196702431</x:v>
+      </x:c>
+      <x:c r="B690" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C690" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D690" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" spans="1:4">
+      <x:c r="A691" s="1">
+        <x:v>46315.6196706134</x:v>
+      </x:c>
+      <x:c r="B691" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C691" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D691" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" spans="1:4">
+      <x:c r="A692" s="1">
+        <x:v>46315.6196709838</x:v>
+      </x:c>
+      <x:c r="B692" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C692" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D692" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" spans="1:4">
+      <x:c r="A693" s="1">
+        <x:v>46315.6196713657</x:v>
+      </x:c>
+      <x:c r="B693" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C693" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D693" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" spans="1:4">
+      <x:c r="A694" s="1">
+        <x:v>46315.619671875</x:v>
+      </x:c>
+      <x:c r="B694" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C694" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D694" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" spans="1:4">
+      <x:c r="A695" s="1">
+        <x:v>46315.6196722569</x:v>
+      </x:c>
+      <x:c r="B695" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C695" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D695" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" spans="1:4">
+      <x:c r="A696" s="1">
+        <x:v>46315.6196727083</x:v>
+      </x:c>
+      <x:c r="B696" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C696" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D696" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" spans="1:4">
+      <x:c r="A697" s="1">
+        <x:v>46315.6196731018</x:v>
+      </x:c>
+      <x:c r="B697" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C697" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D697" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" spans="1:4">
+      <x:c r="A698" s="1">
+        <x:v>46315.6196734722</x:v>
+      </x:c>
+      <x:c r="B698" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C698" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D698" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" spans="1:4">
+      <x:c r="A699" s="1">
+        <x:v>46315.619673831</x:v>
+      </x:c>
+      <x:c r="B699" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C699" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D699" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" spans="1:4">
+      <x:c r="A700" s="1">
+        <x:v>46315.6196744329</x:v>
+      </x:c>
+      <x:c r="B700" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C700" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D700" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" spans="1:4">
+      <x:c r="A701" s="1">
+        <x:v>46315.6196748148</x:v>
+      </x:c>
+      <x:c r="B701" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C701" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D701" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" spans="1:4">
+      <x:c r="A702" s="1">
+        <x:v>46315.6196752778</x:v>
+      </x:c>
+      <x:c r="B702" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C702" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D702" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" spans="1:4">
+      <x:c r="A703" s="1">
+        <x:v>46315.619675706</x:v>
+      </x:c>
+      <x:c r="B703" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C703" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D703" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" spans="1:4">
+      <x:c r="A704" s="1">
+        <x:v>46315.6196760995</x:v>
+      </x:c>
+      <x:c r="B704" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C704" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D704" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" spans="1:4">
+      <x:c r="A705" s="1">
+        <x:v>46315.6196764236</x:v>
+      </x:c>
+      <x:c r="B705" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C705" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D705" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" spans="1:4">
+      <x:c r="A706" s="1">
+        <x:v>46315.6196768287</x:v>
+      </x:c>
+      <x:c r="B706" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C706" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D706" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" spans="1:4">
+      <x:c r="A707" s="1">
+        <x:v>46315.6196772454</x:v>
+      </x:c>
+      <x:c r="B707" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C707" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D707" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" spans="1:4">
+      <x:c r="A708" s="1">
+        <x:v>46315.6196778009</x:v>
+      </x:c>
+      <x:c r="B708" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C708" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D708" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" spans="1:4">
+      <x:c r="A709" s="1">
+        <x:v>46315.6196781944</x:v>
+      </x:c>
+      <x:c r="B709" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C709" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D709" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" spans="1:4">
+      <x:c r="A710" s="1">
+        <x:v>46315.6196785648</x:v>
+      </x:c>
+      <x:c r="B710" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C710" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D710" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" spans="1:4">
+      <x:c r="A711" s="1">
+        <x:v>46315.6196790162</x:v>
+      </x:c>
+      <x:c r="B711" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C711" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D711" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" spans="1:4">
+      <x:c r="A712" s="1">
+        <x:v>46315.6196794213</x:v>
+      </x:c>
+      <x:c r="B712" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C712" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D712" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" spans="1:4">
+      <x:c r="A713" s="1">
+        <x:v>46315.6196797917</x:v>
+      </x:c>
+      <x:c r="B713" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C713" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D713" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" spans="1:4">
+      <x:c r="A714" s="1">
+        <x:v>46315.6196802662</x:v>
+      </x:c>
+      <x:c r="B714" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C714" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D714" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" spans="1:4">
+      <x:c r="A715" s="1">
+        <x:v>46315.6196806597</x:v>
+      </x:c>
+      <x:c r="B715" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C715" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D715" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" spans="1:4">
+      <x:c r="A716" s="1">
+        <x:v>46315.6196810185</x:v>
+      </x:c>
+      <x:c r="B716" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C716" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D716" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" spans="1:4">
+      <x:c r="A717" s="1">
+        <x:v>46315.6196814005</x:v>
+      </x:c>
+      <x:c r="B717" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C717" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D717" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" spans="1:4">
+      <x:c r="A718" s="1">
+        <x:v>46315.6196817708</x:v>
+      </x:c>
+      <x:c r="B718" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C718" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D718" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" spans="1:4">
+      <x:c r="A719" s="1">
+        <x:v>46315.6196821296</x:v>
+      </x:c>
+      <x:c r="B719" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C719" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D719" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720" spans="1:4">
+      <x:c r="A720" s="1">
+        <x:v>46315.6196825231</x:v>
+      </x:c>
+      <x:c r="B720" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C720" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D720" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721" spans="1:4">
+      <x:c r="A721" s="1">
+        <x:v>46315.6196829051</x:v>
+      </x:c>
+      <x:c r="B721" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C721" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D721" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" spans="1:4">
+      <x:c r="A722" s="1">
+        <x:v>46315.6196832639</x:v>
+      </x:c>
+      <x:c r="B722" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C722" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D722" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" spans="1:4">
+      <x:c r="A723" s="1">
+        <x:v>46315.6196836343</x:v>
+      </x:c>
+      <x:c r="B723" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C723" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D723" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" spans="1:4">
+      <x:c r="A724" s="1">
+        <x:v>46315.6196840741</x:v>
+      </x:c>
+      <x:c r="B724" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C724" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D724" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" spans="1:4">
+      <x:c r="A725" s="1">
+        <x:v>46315.6196844329</x:v>
+      </x:c>
+      <x:c r="B725" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C725" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D725" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" spans="1:4">
+      <x:c r="A726" s="1">
+        <x:v>46315.6196848148</x:v>
+      </x:c>
+      <x:c r="B726" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C726" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D726" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" spans="1:4">
+      <x:c r="A727" s="1">
+        <x:v>46315.6196852778</x:v>
+      </x:c>
+      <x:c r="B727" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C727" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D727" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" spans="1:4">
+      <x:c r="A728" s="1">
+        <x:v>46315.6196856597</x:v>
+      </x:c>
+      <x:c r="B728" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C728" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D728" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" spans="1:4">
+      <x:c r="A729" s="1">
+        <x:v>46315.6196860764</x:v>
+      </x:c>
+      <x:c r="B729" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C729" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D729" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" spans="1:4">
+      <x:c r="A730" s="1">
+        <x:v>46315.6196864236</x:v>
+      </x:c>
+      <x:c r="B730" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C730" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D730" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" spans="1:4">
+      <x:c r="A731" s="1">
+        <x:v>46315.619686794</x:v>
+      </x:c>
+      <x:c r="B731" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C731" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D731" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732" spans="1:4">
+      <x:c r="A732" s="1">
+        <x:v>46315.6196872222</x:v>
+      </x:c>
+      <x:c r="B732" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C732" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D732" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="733" spans="1:4">
+      <x:c r="A733" s="1">
+        <x:v>46315.6196877199</x:v>
+      </x:c>
+      <x:c r="B733" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C733" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D733" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" spans="1:4">
+      <x:c r="A734" s="1">
+        <x:v>46315.6196881829</x:v>
+      </x:c>
+      <x:c r="B734" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C734" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D734" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735" spans="1:4">
+      <x:c r="A735" s="1">
+        <x:v>46315.619688588</x:v>
+      </x:c>
+      <x:c r="B735" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C735" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D735" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736" spans="1:4">
+      <x:c r="A736" s="1">
+        <x:v>46315.6196890046</x:v>
+      </x:c>
+      <x:c r="B736" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C736" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D736" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737" spans="1:4">
+      <x:c r="A737" s="1">
+        <x:v>46315.6196893866</x:v>
+      </x:c>
+      <x:c r="B737" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C737" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D737" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738" spans="1:4">
+      <x:c r="A738" s="1">
+        <x:v>46315.6196898032</x:v>
+      </x:c>
+      <x:c r="B738" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C738" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D738" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739" spans="1:4">
+      <x:c r="A739" s="1">
+        <x:v>46315.6196901505</x:v>
+      </x:c>
+      <x:c r="B739" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C739" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D739" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740" spans="1:4">
+      <x:c r="A740" s="1">
+        <x:v>46315.6196905556</x:v>
+      </x:c>
+      <x:c r="B740" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C740" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D740" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741" spans="1:4">
+      <x:c r="A741" s="1">
+        <x:v>46315.6196910185</x:v>
+      </x:c>
+      <x:c r="B741" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C741" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D741" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742" spans="1:4">
+      <x:c r="A742" s="1">
+        <x:v>46315.6196914005</x:v>
+      </x:c>
+      <x:c r="B742" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C742" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D742" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" spans="1:4">
+      <x:c r="A743" s="1">
+        <x:v>46315.619691875</x:v>
+      </x:c>
+      <x:c r="B743" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C743" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D743" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" spans="1:4">
+      <x:c r="A744" s="1">
+        <x:v>46315.6196921759</x:v>
+      </x:c>
+      <x:c r="B744" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C744" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D744" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" spans="1:4">
+      <x:c r="A745" s="1">
+        <x:v>46315.6196925463</x:v>
+      </x:c>
+      <x:c r="B745" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C745" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D745" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" spans="1:4">
+      <x:c r="A746" s="1">
+        <x:v>46315.6196929282</x:v>
+      </x:c>
+      <x:c r="B746" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C746" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D746" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747" spans="1:4">
+      <x:c r="A747" s="1">
+        <x:v>46315.6196932986</x:v>
+      </x:c>
+      <x:c r="B747" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C747" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D747" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748" spans="1:4">
+      <x:c r="A748" s="1">
+        <x:v>46315.619693669</x:v>
+      </x:c>
+      <x:c r="B748" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C748" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D748" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749" spans="1:4">
+      <x:c r="A749" s="1">
+        <x:v>46315.6196941551</x:v>
+      </x:c>
+      <x:c r="B749" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C749" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D749" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750" spans="1:4">
+      <x:c r="A750" s="1">
+        <x:v>46315.619694537</x:v>
+      </x:c>
+      <x:c r="B750" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C750" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D750" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751" spans="1:4">
+      <x:c r="A751" s="1">
+        <x:v>46315.619695</x:v>
+      </x:c>
+      <x:c r="B751" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C751" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D751" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752" spans="1:4">
+      <x:c r="A752" s="1">
+        <x:v>46315.6196953819</x:v>
+      </x:c>
+      <x:c r="B752" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C752" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D752" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753" spans="1:4">
+      <x:c r="A753" s="1">
+        <x:v>46315.619695787</x:v>
+      </x:c>
+      <x:c r="B753" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C753" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D753" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754" spans="1:4">
+      <x:c r="A754" s="1">
+        <x:v>46315.6196962269</x:v>
+      </x:c>
+      <x:c r="B754" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C754" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D754" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" spans="1:4">
+      <x:c r="A755" s="1">
+        <x:v>46315.6196965972</x:v>
+      </x:c>
+      <x:c r="B755" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C755" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D755" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" spans="1:4">
+      <x:c r="A756" s="1">
+        <x:v>46315.6196969792</x:v>
+      </x:c>
+      <x:c r="B756" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C756" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D756" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" spans="1:4">
+      <x:c r="A757" s="1">
+        <x:v>46315.6196973032</x:v>
+      </x:c>
+      <x:c r="B757" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C757" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D757" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" spans="1:4">
+      <x:c r="A758" s="1">
+        <x:v>46315.6196978009</x:v>
+      </x:c>
+      <x:c r="B758" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C758" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D758" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" spans="1:4">
+      <x:c r="A759" s="1">
+        <x:v>46315.6196982292</x:v>
+      </x:c>
+      <x:c r="B759" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C759" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D759" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" spans="1:4">
+      <x:c r="A760" s="1">
+        <x:v>46315.6196985648</x:v>
+      </x:c>
+      <x:c r="B760" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C760" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D760" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" spans="1:4">
+      <x:c r="A761" s="1">
+        <x:v>46315.619698912</x:v>
+      </x:c>
+      <x:c r="B761" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C761" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D761" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" spans="1:4">
+      <x:c r="A762" s="1">
+        <x:v>46315.6196994907</x:v>
+      </x:c>
+      <x:c r="B762" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C762" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D762" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" spans="1:4">
+      <x:c r="A763" s="1">
+        <x:v>46315.619699919</x:v>
+      </x:c>
+      <x:c r="B763" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C763" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D763" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" spans="1:4">
+      <x:c r="A764" s="1">
+        <x:v>46315.6197003125</x:v>
+      </x:c>
+      <x:c r="B764" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C764" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D764" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" spans="1:4">
+      <x:c r="A765" s="1">
+        <x:v>46315.6197006944</x:v>
+      </x:c>
+      <x:c r="B765" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C765" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D765" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" spans="1:4">
+      <x:c r="A766" s="1">
+        <x:v>46315.6197011227</x:v>
+      </x:c>
+      <x:c r="B766" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C766" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D766" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" spans="1:4">
+      <x:c r="A767" s="1">
+        <x:v>46315.6197015394</x:v>
+      </x:c>
+      <x:c r="B767" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C767" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D767" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" spans="1:4">
+      <x:c r="A768" s="1">
+        <x:v>46315.6197019097</x:v>
+      </x:c>
+      <x:c r="B768" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C768" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D768" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" spans="1:4">
+      <x:c r="A769" s="1">
+        <x:v>46315.6197024421</x:v>
+      </x:c>
+      <x:c r="B769" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C769" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D769" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" spans="1:4">
+      <x:c r="A770" s="1">
+        <x:v>46315.6197028241</x:v>
+      </x:c>
+      <x:c r="B770" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C770" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D770" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" spans="1:4">
+      <x:c r="A771" s="1">
+        <x:v>46315.6197032292</x:v>
+      </x:c>
+      <x:c r="B771" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C771" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D771" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" spans="1:4">
+      <x:c r="A772" s="1">
+        <x:v>46315.6197035417</x:v>
+      </x:c>
+      <x:c r="B772" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C772" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D772" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" spans="1:4">
+      <x:c r="A773" s="1">
+        <x:v>46315.6197039699</x:v>
+      </x:c>
+      <x:c r="B773" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C773" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D773" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" spans="1:4">
+      <x:c r="A774" s="1">
+        <x:v>46315.6197043403</x:v>
+      </x:c>
+      <x:c r="B774" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C774" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D774" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" spans="1:4">
+      <x:c r="A775" s="1">
+        <x:v>46315.6197048264</x:v>
+      </x:c>
+      <x:c r="B775" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C775" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D775" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" spans="1:4">
+      <x:c r="A776" s="1">
+        <x:v>46315.6197052083</x:v>
+      </x:c>
+      <x:c r="B776" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C776" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D776" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" spans="1:4">
+      <x:c r="A777" s="1">
+        <x:v>46315.6197055787</x:v>
+      </x:c>
+      <x:c r="B777" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C777" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D777" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" spans="1:4">
+      <x:c r="A778" s="1">
+        <x:v>46315.6197059722</x:v>
+      </x:c>
+      <x:c r="B778" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C778" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D778" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" spans="1:4">
+      <x:c r="A779" s="1">
+        <x:v>46315.6197064931</x:v>
+      </x:c>
+      <x:c r="B779" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C779" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D779" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" spans="1:4">
+      <x:c r="A780" s="1">
+        <x:v>46315.6197069213</x:v>
+      </x:c>
+      <x:c r="B780" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C780" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D780" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" spans="1:4">
+      <x:c r="A781" s="1">
+        <x:v>46315.6197073958</x:v>
+      </x:c>
+      <x:c r="B781" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C781" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D781" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" spans="1:4">
+      <x:c r="A782" s="1">
+        <x:v>46315.6197077778</x:v>
+      </x:c>
+      <x:c r="B782" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C782" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D782" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" spans="1:4">
+      <x:c r="A783" s="1">
+        <x:v>46315.619708206</x:v>
+      </x:c>
+      <x:c r="B783" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C783" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D783" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" spans="1:4">
+      <x:c r="A784" s="1">
+        <x:v>46315.6197086227</x:v>
+      </x:c>
+      <x:c r="B784" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C784" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D784" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" spans="1:4">
+      <x:c r="A785" s="1">
+        <x:v>46315.6197092361</x:v>
+      </x:c>
+      <x:c r="B785" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C785" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D785" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" spans="1:4">
+      <x:c r="A786" s="1">
+        <x:v>46315.619710081</x:v>
+      </x:c>
+      <x:c r="B786" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C786" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D786" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" spans="1:4">
+      <x:c r="A787" s="1">
+        <x:v>46315.619710463</x:v>
+      </x:c>
+      <x:c r="B787" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C787" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D787" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" spans="1:4">
+      <x:c r="A788" s="1">
+        <x:v>46315.6197108449</x:v>
+      </x:c>
+      <x:c r="B788" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C788" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D788" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" spans="1:4">
+      <x:c r="A789" s="1">
+        <x:v>46315.6197112268</x:v>
+      </x:c>
+      <x:c r="B789" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C789" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D789" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" spans="1:4">
+      <x:c r="A790" s="1">
+        <x:v>46315.6197116204</x:v>
+      </x:c>
+      <x:c r="B790" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C790" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D790" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" spans="1:4">
+      <x:c r="A791" s="1">
+        <x:v>46315.6197120023</x:v>
+      </x:c>
+      <x:c r="B791" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C791" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D791" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" spans="1:4">
+      <x:c r="A792" s="1">
+        <x:v>46315.6197123843</x:v>
+      </x:c>
+      <x:c r="B792" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C792" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D792" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" spans="1:4">
+      <x:c r="A793" s="1">
+        <x:v>46315.6197127546</x:v>
+      </x:c>
+      <x:c r="B793" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C793" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D793" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" spans="1:4">
+      <x:c r="A794" s="1">
+        <x:v>46315.6197131713</x:v>
+      </x:c>
+      <x:c r="B794" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C794" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D794" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" spans="1:4">
+      <x:c r="A795" s="1">
+        <x:v>46315.6197136806</x:v>
+      </x:c>
+      <x:c r="B795" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C795" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D795" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" spans="1:4">
+      <x:c r="A796" s="1">
+        <x:v>46315.6197141088</x:v>
+      </x:c>
+      <x:c r="B796" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C796" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D796" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" spans="1:4">
+      <x:c r="A797" s="1">
+        <x:v>46315.6197146412</x:v>
+      </x:c>
+      <x:c r="B797" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C797" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D797" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" spans="1:4">
+      <x:c r="A798" s="1">
+        <x:v>46315.6197150231</x:v>
+      </x:c>
+      <x:c r="B798" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C798" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D798" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" spans="1:4">
+      <x:c r="A799" s="1">
+        <x:v>46315.6197153935</x:v>
+      </x:c>
+      <x:c r="B799" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C799" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D799" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" spans="1:4">
+      <x:c r="A800" s="1">
+        <x:v>46315.6197157523</x:v>
+      </x:c>
+      <x:c r="B800" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C800" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D800" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" spans="1:4">
+      <x:c r="A801" s="1">
+        <x:v>46315.6197161574</x:v>
+      </x:c>
+      <x:c r="B801" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C801" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D801" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" spans="1:4">
+      <x:c r="A802" s="1">
+        <x:v>46315.6197166088</x:v>
+      </x:c>
+      <x:c r="B802" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C802" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D802" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" spans="1:4">
+      <x:c r="A803" s="1">
+        <x:v>46315.6197170833</x:v>
+      </x:c>
+      <x:c r="B803" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C803" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D803" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" spans="1:4">
+      <x:c r="A804" s="1">
+        <x:v>46315.6197174769</x:v>
+      </x:c>
+      <x:c r="B804" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C804" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D804" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" spans="1:4">
+      <x:c r="A805" s="1">
+        <x:v>46315.6197178588</x:v>
+      </x:c>
+      <x:c r="B805" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C805" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D805" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" spans="1:4">
+      <x:c r="A806" s="1">
+        <x:v>46315.6197182407</x:v>
+      </x:c>
+      <x:c r="B806" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C806" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D806" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" spans="1:4">
+      <x:c r="A807" s="1">
+        <x:v>46315.6197186227</x:v>
+      </x:c>
+      <x:c r="B807" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C807" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D807" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" spans="1:4">
+      <x:c r="A808" s="1">
+        <x:v>46315.6197189931</x:v>
+      </x:c>
+      <x:c r="B808" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C808" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D808" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" spans="1:4">
+      <x:c r="A809" s="1">
+        <x:v>46315.6197194444</x:v>
+      </x:c>
+      <x:c r="B809" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C809" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D809" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" spans="1:4">
+      <x:c r="A810" s="1">
+        <x:v>46315.619719838</x:v>
+      </x:c>
+      <x:c r="B810" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C810" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D810" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" spans="1:4">
+      <x:c r="A811" s="1">
+        <x:v>46315.6197202199</x:v>
+      </x:c>
+      <x:c r="B811" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C811" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D811" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" spans="1:4">
+      <x:c r="A812" s="1">
+        <x:v>46315.6197206944</x:v>
+      </x:c>
+      <x:c r="B812" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C812" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D812" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" spans="1:4">
+      <x:c r="A813" s="1">
+        <x:v>46315.6197210764</x:v>
+      </x:c>
+      <x:c r="B813" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C813" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D813" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" spans="1:4">
+      <x:c r="A814" s="1">
+        <x:v>46315.6197214352</x:v>
+      </x:c>
+      <x:c r="B814" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C814" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D814" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" spans="1:4">
+      <x:c r="A815" s="1">
+        <x:v>46315.6197218403</x:v>
+      </x:c>
+      <x:c r="B815" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C815" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D815" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" spans="1:4">
+      <x:c r="A816" s="1">
+        <x:v>46315.6197222685</x:v>
+      </x:c>
+      <x:c r="B816" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C816" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D816" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" spans="1:4">
+      <x:c r="A817" s="1">
+        <x:v>46315.6197226389</x:v>
+      </x:c>
+      <x:c r="B817" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C817" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D817" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" spans="1:4">
+      <x:c r="A818" s="1">
+        <x:v>46315.6197230208</x:v>
+      </x:c>
+      <x:c r="B818" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C818" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D818" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" spans="1:4">
+      <x:c r="A819" s="1">
+        <x:v>46315.6197234144</x:v>
+      </x:c>
+      <x:c r="B819" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C819" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D819" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" spans="1:4">
+      <x:c r="A820" s="1">
+        <x:v>46315.6197237847</x:v>
+      </x:c>
+      <x:c r="B820" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C820" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D820" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" spans="1:4">
+      <x:c r="A821" s="1">
+        <x:v>46315.6197242708</x:v>
+      </x:c>
+      <x:c r="B821" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C821" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D821" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822" spans="1:4">
+      <x:c r="A822" s="1">
+        <x:v>46315.6197246296</x:v>
+      </x:c>
+      <x:c r="B822" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C822" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D822" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823" spans="1:4">
+      <x:c r="A823" s="1">
+        <x:v>46315.619725</x:v>
+      </x:c>
+      <x:c r="B823" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C823" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D823" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824" spans="1:4">
+      <x:c r="A824" s="1">
+        <x:v>46315.6197253819</x:v>
+      </x:c>
+      <x:c r="B824" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C824" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D824" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825" spans="1:4">
+      <x:c r="A825" s="1">
+        <x:v>46315.6197257755</x:v>
+      </x:c>
+      <x:c r="B825" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C825" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D825" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826" spans="1:4">
+      <x:c r="A826" s="1">
+        <x:v>46315.6197261343</x:v>
+      </x:c>
+      <x:c r="B826" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C826" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D826" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827" spans="1:4">
+      <x:c r="A827" s="1">
+        <x:v>46315.6197266088</x:v>
+      </x:c>
+      <x:c r="B827" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C827" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D827" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828" spans="1:4">
+      <x:c r="A828" s="1">
+        <x:v>46315.6197270023</x:v>
+      </x:c>
+      <x:c r="B828" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C828" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D828" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829" spans="1:4">
+      <x:c r="A829" s="1">
+        <x:v>46315.6197273727</x:v>
+      </x:c>
+      <x:c r="B829" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C829" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D829" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830" spans="1:4">
+      <x:c r="A830" s="1">
+        <x:v>46315.6197277662</x:v>
+      </x:c>
+      <x:c r="B830" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C830" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D830" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831" spans="1:4">
+      <x:c r="A831" s="1">
+        <x:v>46315.6197281366</x:v>
+      </x:c>
+      <x:c r="B831" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C831" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D831" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832" spans="1:4">
+      <x:c r="A832" s="1">
+        <x:v>46315.6197285069</x:v>
+      </x:c>
+      <x:c r="B832" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C832" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D832" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833" spans="1:4">
+      <x:c r="A833" s="1">
+        <x:v>46315.6197288889</x:v>
+      </x:c>
+      <x:c r="B833" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C833" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D833" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834" spans="1:4">
+      <x:c r="A834" s="1">
+        <x:v>46315.6197293403</x:v>
+      </x:c>
+      <x:c r="B834" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C834" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D834" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835" spans="1:4">
+      <x:c r="A835" s="1">
+        <x:v>46315.6197297106</x:v>
+      </x:c>
+      <x:c r="B835" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C835" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D835" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836" spans="1:4">
+      <x:c r="A836" s="1">
+        <x:v>46315.619730081</x:v>
+      </x:c>
+      <x:c r="B836" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C836" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D836" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837" spans="1:4">
+      <x:c r="A837" s="1">
+        <x:v>46315.6197305208</x:v>
+      </x:c>
+      <x:c r="B837" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C837" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D837" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838" spans="1:4">
+      <x:c r="A838" s="1">
+        <x:v>46315.6197309491</x:v>
+      </x:c>
+      <x:c r="B838" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C838" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D838" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839" spans="1:4">
+      <x:c r="A839" s="1">
+        <x:v>46315.6197313079</x:v>
+      </x:c>
+      <x:c r="B839" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C839" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D839" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="840" spans="1:4">
+      <x:c r="A840" s="1">
+        <x:v>46315.6197318056</x:v>
+      </x:c>
+      <x:c r="B840" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C840" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D840" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841" spans="1:4">
+      <x:c r="A841" s="1">
+        <x:v>46315.6197322801</x:v>
+      </x:c>
+      <x:c r="B841" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C841" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D841" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842" spans="1:4">
+      <x:c r="A842" s="1">
+        <x:v>46315.6197326852</x:v>
+      </x:c>
+      <x:c r="B842" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C842" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D842" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843" spans="1:4">
+      <x:c r="A843" s="1">
+        <x:v>46315.6197330556</x:v>
+      </x:c>
+      <x:c r="B843" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C843" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D843" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844" spans="1:4">
+      <x:c r="A844" s="1">
+        <x:v>46315.6197334375</x:v>
+      </x:c>
+      <x:c r="B844" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C844" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D844" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845" spans="1:4">
+      <x:c r="A845" s="1">
+        <x:v>46315.6197338194</x:v>
+      </x:c>
+      <x:c r="B845" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C845" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D845" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846" spans="1:4">
+      <x:c r="A846" s="1">
+        <x:v>46315.6197341898</x:v>
+      </x:c>
+      <x:c r="B846" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C846" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D846" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847" spans="1:4">
+      <x:c r="A847" s="1">
+        <x:v>46315.6197345949</x:v>
+      </x:c>
+      <x:c r="B847" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C847" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D847" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848" spans="1:4">
+      <x:c r="A848" s="1">
+        <x:v>46315.6197349653</x:v>
+      </x:c>
+      <x:c r="B848" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C848" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D848" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849" spans="1:4">
+      <x:c r="A849" s="1">
+        <x:v>46315.6197353356</x:v>
+      </x:c>
+      <x:c r="B849" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C849" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D849" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850" spans="1:4">
+      <x:c r="A850" s="1">
+        <x:v>46315.6197357407</x:v>
+      </x:c>
+      <x:c r="B850" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C850" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D850" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851" spans="1:4">
+      <x:c r="A851" s="1">
+        <x:v>46315.6197361574</x:v>
+      </x:c>
+      <x:c r="B851" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C851" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D851" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852" spans="1:4">
+      <x:c r="A852" s="1">
+        <x:v>46315.6197365856</x:v>
+      </x:c>
+      <x:c r="B852" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C852" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D852" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853" spans="1:4">
+      <x:c r="A853" s="1">
+        <x:v>46315.6197369329</x:v>
+      </x:c>
+      <x:c r="B853" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C853" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D853" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854" spans="1:4">
+      <x:c r="A854" s="1">
+        <x:v>46315.6197373148</x:v>
+      </x:c>
+      <x:c r="B854" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C854" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D854" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855" spans="1:4">
+      <x:c r="A855" s="1">
+        <x:v>46315.6197376736</x:v>
+      </x:c>
+      <x:c r="B855" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C855" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D855" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856" spans="1:4">
+      <x:c r="A856" s="1">
+        <x:v>46315.6197381134</x:v>
+      </x:c>
+      <x:c r="B856" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C856" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D856" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857" spans="1:4">
+      <x:c r="A857" s="1">
+        <x:v>46315.6197384954</x:v>
+      </x:c>
+      <x:c r="B857" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C857" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D857" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858" spans="1:4">
+      <x:c r="A858" s="1">
+        <x:v>46315.6197388542</x:v>
+      </x:c>
+      <x:c r="B858" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C858" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D858" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="859" spans="1:4">
+      <x:c r="A859" s="1">
+        <x:v>46315.6197393171</x:v>
+      </x:c>
+      <x:c r="B859" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C859" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D859" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860" spans="1:4">
+      <x:c r="A860" s="1">
+        <x:v>46315.6197396875</x:v>
+      </x:c>
+      <x:c r="B860" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C860" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D860" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861" spans="1:4">
+      <x:c r="A861" s="1">
+        <x:v>46315.6197400579</x:v>
+      </x:c>
+      <x:c r="B861" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C861" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D861" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862" spans="1:4">
+      <x:c r="A862" s="1">
+        <x:v>46315.6197404282</x:v>
+      </x:c>
+      <x:c r="B862" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C862" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D862" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863" spans="1:4">
+      <x:c r="A863" s="1">
+        <x:v>46315.6197407986</x:v>
+      </x:c>
+      <x:c r="B863" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C863" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D863" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864" spans="1:4">
+      <x:c r="A864" s="1">
+        <x:v>46315.619741169</x:v>
+      </x:c>
+      <x:c r="B864" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C864" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D864" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865" spans="1:4">
+      <x:c r="A865" s="1">
+        <x:v>46315.6197416319</x:v>
+      </x:c>
+      <x:c r="B865" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C865" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D865" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866" spans="1:4">
+      <x:c r="A866" s="1">
+        <x:v>46315.6197420255</x:v>
+      </x:c>
+      <x:c r="B866" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C866" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D866" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867" spans="1:4">
+      <x:c r="A867" s="1">
+        <x:v>46315.6197423958</x:v>
+      </x:c>
+      <x:c r="B867" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C867" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D867" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868" spans="1:4">
+      <x:c r="A868" s="1">
+        <x:v>46315.6197427778</x:v>
+      </x:c>
+      <x:c r="B868" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C868" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D868" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869" spans="1:4">
+      <x:c r="A869" s="1">
+        <x:v>46315.6197431944</x:v>
+      </x:c>
+      <x:c r="B869" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C869" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D869" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870" spans="1:4">
+      <x:c r="A870" s="1">
+        <x:v>46315.6197437384</x:v>
+      </x:c>
+      <x:c r="B870" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C870" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D870" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871" spans="1:4">
+      <x:c r="A871" s="1">
+        <x:v>46315.6197441898</x:v>
+      </x:c>
+      <x:c r="B871" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C871" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D871" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872" spans="1:4">
+      <x:c r="A872" s="1">
+        <x:v>46315.6197445718</x:v>
+      </x:c>
+      <x:c r="B872" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C872" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D872" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873" spans="1:4">
+      <x:c r="A873" s="1">
+        <x:v>46315.6197449537</x:v>
+      </x:c>
+      <x:c r="B873" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C873" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D873" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874" spans="1:4">
+      <x:c r="A874" s="1">
+        <x:v>46315.6197453819</x:v>
+      </x:c>
+      <x:c r="B874" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C874" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D874" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875" spans="1:4">
+      <x:c r="A875" s="1">
+        <x:v>46315.6197457755</x:v>
+      </x:c>
+      <x:c r="B875" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C875" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D875" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876" spans="1:4">
+      <x:c r="A876" s="1">
+        <x:v>46315.6197461458</x:v>
+      </x:c>
+      <x:c r="B876" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C876" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D876" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877" spans="1:4">
+      <x:c r="A877" s="1">
+        <x:v>46315.6197466435</x:v>
+      </x:c>
+      <x:c r="B877" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C877" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D877" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="878" spans="1:4">
+      <x:c r="A878" s="1">
+        <x:v>46315.6197470139</x:v>
+      </x:c>
+      <x:c r="B878" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C878" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D878" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879" spans="1:4">
+      <x:c r="A879" s="1">
+        <x:v>46315.619747419</x:v>
+      </x:c>
+      <x:c r="B879" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C879" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D879" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880" spans="1:4">
+      <x:c r="A880" s="1">
+        <x:v>46315.6197477894</x:v>
+      </x:c>
+      <x:c r="B880" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C880" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D880" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881" spans="1:4">
+      <x:c r="A881" s="1">
+        <x:v>46315.6197482986</x:v>
+      </x:c>
+      <x:c r="B881" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C881" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D881" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882" spans="1:4">
+      <x:c r="A882" s="1">
+        <x:v>46315.6197487037</x:v>
+      </x:c>
+      <x:c r="B882" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C882" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D882" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883" spans="1:4">
+      <x:c r="A883" s="1">
+        <x:v>46315.6197491782</x:v>
+      </x:c>
+      <x:c r="B883" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C883" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D883" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884" spans="1:4">
+      <x:c r="A884" s="1">
+        <x:v>46315.6197495602</x:v>
+      </x:c>
+      <x:c r="B884" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C884" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D884" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885" spans="1:4">
+      <x:c r="A885" s="1">
+        <x:v>46315.6197499537</x:v>
+      </x:c>
+      <x:c r="B885" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C885" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D885" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886" spans="1:4">
+      <x:c r="A886" s="1">
+        <x:v>46315.6197503704</x:v>
+      </x:c>
+      <x:c r="B886" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C886" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D886" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887" spans="1:4">
+      <x:c r="A887" s="1">
+        <x:v>46315.6197507407</x:v>
+      </x:c>
+      <x:c r="B887" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C887" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D887" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888" spans="1:4">
+      <x:c r="A888" s="1">
+        <x:v>46315.6197511343</x:v>
+      </x:c>
+      <x:c r="B888" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C888" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D888" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889" spans="1:4">
+      <x:c r="A889" s="1">
+        <x:v>46315.6197515972</x:v>
+      </x:c>
+      <x:c r="B889" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C889" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D889" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890" spans="1:4">
+      <x:c r="A890" s="1">
+        <x:v>46315.6197519792</x:v>
+      </x:c>
+      <x:c r="B890" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C890" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D890" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891" spans="1:4">
+      <x:c r="A891" s="1">
+        <x:v>46315.6197523843</x:v>
+      </x:c>
+      <x:c r="B891" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C891" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D891" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892" spans="1:4">
+      <x:c r="A892" s="1">
+        <x:v>46315.6197527431</x:v>
+      </x:c>
+      <x:c r="B892" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C892" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D892" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893" spans="1:4">
+      <x:c r="A893" s="1">
+        <x:v>46315.6197531366</x:v>
+      </x:c>
+      <x:c r="B893" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C893" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D893" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894" spans="1:4">
+      <x:c r="A894" s="1">
+        <x:v>46315.6197535069</x:v>
+      </x:c>
+      <x:c r="B894" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C894" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D894" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895" spans="1:4">
+      <x:c r="A895" s="1">
+        <x:v>46315.6197538889</x:v>
+      </x:c>
+      <x:c r="B895" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C895" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D895" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896" spans="1:4">
+      <x:c r="A896" s="1">
+        <x:v>46315.6197542593</x:v>
+      </x:c>
+      <x:c r="B896" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C896" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D896" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897" spans="1:4">
+      <x:c r="A897" s="1">
+        <x:v>46315.6197546412</x:v>
+      </x:c>
+      <x:c r="B897" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C897" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D897" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898" spans="1:4">
+      <x:c r="A898" s="1">
+        <x:v>46315.6197550579</x:v>
+      </x:c>
+      <x:c r="B898" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C898" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D898" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899" spans="1:4">
+      <x:c r="A899" s="1">
+        <x:v>46315.6197553819</x:v>
+      </x:c>
+      <x:c r="B899" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C899" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D899" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
